--- a/data/trans_dic/IP2907_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial</t>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,08</t>
+          <t>8,4; 20,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,69; 35,38</t>
+          <t>15,73; 34,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,46; 25,26</t>
+          <t>13,96; 25,98</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 22,91</t>
+          <t>10,53; 23,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 27,56</t>
+          <t>13,45; 28,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,31; 23,06</t>
+          <t>13,48; 22,73</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 28,74</t>
+          <t>10,4; 28,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 23,16</t>
+          <t>7,16; 21,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,63; 22,36</t>
+          <t>9,93; 21,86</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,82; 27,42</t>
+          <t>17,26; 27,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,13; 26,73</t>
+          <t>14,67; 26,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,17; 25,31</t>
+          <t>17,6; 25,65</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,57; 26,2</t>
+          <t>13,43; 25,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 24,97</t>
+          <t>12,7; 25,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,72; 24,33</t>
+          <t>14,74; 23,47</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,05; 33,39</t>
+          <t>15,77; 32,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,8; 33,95</t>
+          <t>13,81; 33,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,21; 29,89</t>
+          <t>16,81; 29,15</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,22; 21,59</t>
+          <t>16,28; 21,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,86; 23,02</t>
+          <t>16,76; 23,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,36; 21,62</t>
+          <t>17,49; 21,75</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>13100</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29860</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42960</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8414; 20467</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20869; 45885</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32496; 60489</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>15178</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18396</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33574</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>9831; 22256</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12544; 26152</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>25151; 42425</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8838</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8408</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17246</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>5037; 13672</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4436; 13596</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10960; 24134</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>40466</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42334</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>82800</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>31894; 50853</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30950; 56084</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69639; 101521</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>22047</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29361</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>51408</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>15417; 29625</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20067; 40484</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>40206; 64040</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>15425</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15056</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>30481</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>10628; 22175</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9398; 22527</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>22774; 39492</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>115054</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>143414</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>258467</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>99128; 132162</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>121508; 169765</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>233330; 290111</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2907_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 20,44</t>
+          <t>7,98; 20,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,73; 34,59</t>
+          <t>15,35; 33,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,96; 25,98</t>
+          <t>13,9; 25,3</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 23,83</t>
+          <t>11,13; 23,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,45; 28,05</t>
+          <t>13,27; 28,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,48; 22,73</t>
+          <t>13,89; 23,28</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 28,22</t>
+          <t>10,82; 28,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 21,94</t>
+          <t>6,92; 22,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 21,86</t>
+          <t>10,49; 22,35</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 27,51</t>
+          <t>17,32; 27,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,67; 26,59</t>
+          <t>14,99; 26,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,6; 25,65</t>
+          <t>17,43; 25,37</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,43; 25,81</t>
+          <t>14,04; 26,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,7; 25,61</t>
+          <t>12,47; 25,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,74; 23,47</t>
+          <t>14,31; 23,54</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,77; 32,91</t>
+          <t>14,75; 32,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,81; 33,09</t>
+          <t>13,6; 33,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,81; 29,15</t>
+          <t>16,24; 29,31</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,28; 21,7</t>
+          <t>16,2; 21,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,76; 23,42</t>
+          <t>16,83; 23,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,49; 21,75</t>
+          <t>17,64; 21,67</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8414; 20467</t>
+          <t>7987; 20066</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20869; 45885</t>
+          <t>20360; 44899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32496; 60489</t>
+          <t>32358; 58907</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9831; 22256</t>
+          <t>10392; 21947</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12544; 26152</t>
+          <t>12372; 26437</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25151; 42425</t>
+          <t>25931; 43450</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5037; 13672</t>
+          <t>5241; 13830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4436; 13596</t>
+          <t>4292; 14218</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10960; 24134</t>
+          <t>11581; 24682</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31894; 50853</t>
+          <t>32015; 50961</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30950; 56084</t>
+          <t>31608; 55071</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69639; 101521</t>
+          <t>68985; 100384</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15417; 29625</t>
+          <t>16117; 30496</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20067; 40484</t>
+          <t>19711; 40476</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40206; 64040</t>
+          <t>39033; 64235</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10628; 22175</t>
+          <t>9938; 21786</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9398; 22527</t>
+          <t>9254; 22703</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22774; 39492</t>
+          <t>22004; 39698</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>99128; 132162</t>
+          <t>98657; 130526</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>121508; 169765</t>
+          <t>122005; 167452</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>233330; 290111</t>
+          <t>235315; 289077</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2907_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,98; 20,04</t>
+          <t>13,83; 27,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,35; 33,84</t>
+          <t>8,44; 20,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,9; 25,3</t>
+          <t>12,65; 21,12</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 23,5</t>
+          <t>12,77; 27,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,27; 28,35</t>
+          <t>10,34; 22,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,89; 23,28</t>
+          <t>12,92; 22,48</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,82; 28,55</t>
+          <t>8,19; 24,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 22,94</t>
+          <t>9,85; 28,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,49; 22,35</t>
+          <t>10,93; 23,58</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,32; 27,57</t>
+          <t>14,65; 27,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,99; 26,11</t>
+          <t>17,99; 28,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 25,37</t>
+          <t>17,3; 25,5</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 26,56</t>
+          <t>12,76; 24,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,47; 25,61</t>
+          <t>13,38; 25,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,31; 23,54</t>
+          <t>14,65; 23,99</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,75; 32,33</t>
+          <t>14,21; 33,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,6; 33,35</t>
+          <t>16,07; 33,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,24; 29,31</t>
+          <t>17,14; 29,44</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,2; 21,43</t>
+          <t>16,42; 22,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,83; 23,1</t>
+          <t>16,43; 21,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,64; 21,67</t>
+          <t>17,2; 21,31</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23372</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>13100</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>29860</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42960</t>
+          <t>36473</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7987; 20066</t>
+          <t>16429; 32236</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20360; 44899</t>
+          <t>8337; 20073</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32358; 58907</t>
+          <t>27524; 45944</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>17289</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33574</t>
+          <t>32626</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10392; 21947</t>
+          <t>11422; 24162</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12372; 26437</t>
+          <t>9870; 21885</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25931; 43450</t>
+          <t>23878; 41553</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8408</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>16984</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5241; 13830</t>
+          <t>4551; 13715</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4292; 14218</t>
+          <t>4897; 14128</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11581; 24682</t>
+          <t>11508; 24819</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>40466</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42334</t>
+          <t>39153</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82800</t>
+          <t>77591</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32015; 50961</t>
+          <t>28656; 52875</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31608; 55071</t>
+          <t>30556; 48278</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68985; 100384</t>
+          <t>63220; 93197</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>26798</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51408</t>
+          <t>48567</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16117; 30496</t>
+          <t>18396; 35917</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19711; 40476</t>
+          <t>15337; 29729</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39033; 64235</t>
+          <t>37909; 62068</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15771</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30481</t>
+          <t>30127</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9938; 21786</t>
+          <t>9222; 22064</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9254; 22703</t>
+          <t>11052; 22874</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22004; 39698</t>
+          <t>22913; 39356</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>173</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>115054</t>
+          <t>128397</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>143414</t>
+          <t>113972</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258467</t>
+          <t>242368</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>98657; 130526</t>
+          <t>109737; 149043</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>122005; 167452</t>
+          <t>98092; 130207</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>235315; 289077</t>
+          <t>217680; 269679</t>
         </is>
       </c>
     </row>
